--- a/astro-site/public/dl/seafood-restaurant-checklist-templates/07-seafood-restaurant-weekly-monthly-checklist.xlsx
+++ b/astro-site/public/dl/seafood-restaurant-checklist-templates/07-seafood-restaurant-weekly-monthly-checklist.xlsx
@@ -788,7 +788,7 @@
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="33.25" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Weekly</t>
@@ -796,7 +796,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Check white wine and Albarino stock</t>
+          <t>Check white wine stock (Albariño, Sauvignon Blanc, Muscadet, Chablis)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
